--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run3/epoch_40/per_file_predictions_epoch_40.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run3/epoch_40/per_file_predictions_epoch_40.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.5887,0.0196,0.1415,0.2192</t>
-  </si>
-  <si>
-    <t>0.0022,0.0025,0.0005,0.9986</t>
-  </si>
-  <si>
-    <t>0.8226,0.0268,0.0535,0.0807</t>
-  </si>
-  <si>
-    <t>0.0318,0.0091,0.0014,0.9878</t>
-  </si>
-  <si>
-    <t>0.9919,0.0041,0.0008,0.0012</t>
-  </si>
-  <si>
-    <t>0.9945,0.0021,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9914,0.0045,0.0012,0.0013</t>
-  </si>
-  <si>
-    <t>0.9897,0.0049,0.0016,0.0021</t>
-  </si>
-  <si>
-    <t>0.9875,0.0083,0.0008,0.0012</t>
-  </si>
-  <si>
-    <t>0.9880,0.0068,0.0011,0.0021</t>
-  </si>
-  <si>
-    <t>0.9973,0.0009,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9831,0.0079,0.0013,0.0039</t>
-  </si>
-  <si>
-    <t>0.6625,0.0174,0.3760,0.0097</t>
-  </si>
-  <si>
-    <t>0.6001,0.0104,0.5161,0.0033</t>
-  </si>
-  <si>
-    <t>0.5890,0.0193,0.4620,0.0113</t>
-  </si>
-  <si>
-    <t>0.1934,0.0456,0.7872,0.0098</t>
-  </si>
-  <si>
-    <t>0.5601,0.0697,0.4156,0.0154</t>
-  </si>
-  <si>
-    <t>0.0274,0.9450,0.1240,0.0008</t>
-  </si>
-  <si>
-    <t>0.0113,0.9785,0.0205,0.0003</t>
-  </si>
-  <si>
-    <t>0.5943,0.4869,0.0081,0.0057</t>
-  </si>
-  <si>
-    <t>0.2704,0.7793,0.0154,0.0036</t>
-  </si>
-  <si>
-    <t>0.0251,0.9721,0.0063,0.0002</t>
-  </si>
-  <si>
-    <t>0.5752,0.0081,0.4957,0.0083</t>
-  </si>
-  <si>
-    <t>0.5552,0.0226,0.4583,0.0194</t>
-  </si>
-  <si>
-    <t>0.1848,0.0057,0.8636,0.0075</t>
-  </si>
-  <si>
-    <t>0.4236,0.0091,0.6339,0.0114</t>
-  </si>
-  <si>
-    <t>0.1672,0.0049,0.8768,0.0102</t>
-  </si>
-  <si>
-    <t>0.0555,0.0364,0.6518,0.3326</t>
-  </si>
-  <si>
-    <t>0.0039,0.0034,0.9854,0.0118</t>
-  </si>
-  <si>
-    <t>0.6846,0.2514,0.0952,0.0049</t>
-  </si>
-  <si>
-    <t>0.4865,0.3384,0.2512,0.0323</t>
-  </si>
-  <si>
-    <t>0.0092,0.0101,0.9777,0.0098</t>
-  </si>
-  <si>
-    <t>0.0380,0.8926,0.2566,0.0121</t>
-  </si>
-  <si>
-    <t>0.5914,0.3507,0.1528,0.0208</t>
-  </si>
-  <si>
-    <t>0.5604,0.0692,0.4034,0.0089</t>
-  </si>
-  <si>
-    <t>0.6578,0.3871,0.0345,0.0017</t>
-  </si>
-  <si>
-    <t>0.0356,0.8809,0.3440,0.0017</t>
-  </si>
-  <si>
-    <t>0.0465,0.2732,0.8331,0.0093</t>
-  </si>
-  <si>
-    <t>0.1049,0.0968,0.8390,0.0115</t>
-  </si>
-  <si>
-    <t>0.1468,0.0594,0.8233,0.0099</t>
-  </si>
-  <si>
-    <t>0.3431,0.0087,0.5106,0.0673</t>
-  </si>
-  <si>
-    <t>0.1354,0.0685,0.8259,0.0129</t>
-  </si>
-  <si>
-    <t>0.0109,0.9535,0.0770,0.0003</t>
-  </si>
-  <si>
-    <t>0.1503,0.0129,0.8383,0.0259</t>
-  </si>
-  <si>
-    <t>0.0332,0.5906,0.0239,0.9043</t>
-  </si>
-  <si>
-    <t>0.0178,0.9501,0.0410,0.0168</t>
-  </si>
-  <si>
-    <t>0.0092,0.8898,0.5358,0.0036</t>
-  </si>
-  <si>
-    <t>0.0017,0.9851,0.0812,0.0080</t>
-  </si>
-  <si>
-    <t>0.0170,0.1281,0.9471,0.0043</t>
-  </si>
-  <si>
-    <t>0.0053,0.3463,0.9464,0.0030</t>
-  </si>
-  <si>
-    <t>0.0961,0.0056,0.9079,0.0109</t>
-  </si>
-  <si>
-    <t>0.0404,0.0066,0.9457,0.0154</t>
-  </si>
-  <si>
-    <t>0.0108,0.0124,0.9759,0.0054</t>
-  </si>
-  <si>
-    <t>0.0211,0.0332,0.9646,0.0042</t>
-  </si>
-  <si>
-    <t>0.9735,0.0326,0.0031,0.0009</t>
-  </si>
-  <si>
-    <t>0.9693,0.0252,0.0042,0.0047</t>
-  </si>
-  <si>
-    <t>0.9490,0.0381,0.0076,0.0111</t>
-  </si>
-  <si>
-    <t>0.0314,0.2161,0.9323,0.0169</t>
-  </si>
-  <si>
-    <t>0.9756,0.0146,0.0023,0.0065</t>
-  </si>
-  <si>
-    <t>0.9871,0.0088,0.0013,0.0015</t>
-  </si>
-  <si>
-    <t>0.9926,0.0045,0.0006,0.0007</t>
-  </si>
-  <si>
-    <t>0.0034,0.9377,0.6014,0.0011</t>
-  </si>
-  <si>
-    <t>0.0095,0.0841,0.9699,0.0038</t>
-  </si>
-  <si>
-    <t>0.0911,0.0251,0.8806,0.0279</t>
-  </si>
-  <si>
-    <t>0.0041,0.7358,0.8891,0.0008</t>
-  </si>
-  <si>
-    <t>0.0071,0.0104,0.9884,0.0010</t>
-  </si>
-  <si>
-    <t>0.1886,0.7785,0.0343,0.0021</t>
-  </si>
-  <si>
-    <t>0.0406,0.9617,0.0034,0.0003</t>
-  </si>
-  <si>
-    <t>0.3976,0.0422,0.6511,0.0179</t>
-  </si>
-  <si>
-    <t>0.3308,0.0686,0.6306,0.0044</t>
-  </si>
-  <si>
-    <t>0.0057,0.0143,0.9798,0.0127</t>
-  </si>
-  <si>
-    <t>0.0008,0.9503,0.7793,0.0003</t>
-  </si>
-  <si>
-    <t>0.0129,0.5408,0.8808,0.0015</t>
-  </si>
-  <si>
-    <t>0.0028,0.9763,0.0844,0.0007</t>
-  </si>
-  <si>
-    <t>0.0013,0.9744,0.2664,0.0006</t>
-  </si>
-  <si>
-    <t>0.0235,0.0016,0.0497,0.9410</t>
-  </si>
-  <si>
-    <t>0.0094,0.0035,0.0042,0.9929</t>
-  </si>
-  <si>
-    <t>0.0082,0.0082,0.0045,0.9918</t>
-  </si>
-  <si>
-    <t>0.0036,0.0050,0.0009,0.9975</t>
-  </si>
-  <si>
-    <t>0.0186,0.0294,0.0086,0.9855</t>
-  </si>
-  <si>
-    <t>0.0050,0.0019,0.0063,0.9935</t>
-  </si>
-  <si>
-    <t>0.0019,0.7709,0.8696,0.0002</t>
-  </si>
-  <si>
-    <t>0.0146,0.3685,0.9157,0.0047</t>
-  </si>
-  <si>
-    <t>0.0181,0.2283,0.9216,0.0041</t>
-  </si>
-  <si>
-    <t>0.0131,0.2581,0.9174,0.0016</t>
-  </si>
-  <si>
-    <t>0.0018,0.8443,0.7702,0.0001</t>
-  </si>
-  <si>
-    <t>0.0049,0.6849,0.8651,0.0011</t>
-  </si>
-  <si>
-    <t>0.9779,0.0091,0.0028,0.0051</t>
-  </si>
-  <si>
-    <t>0.9909,0.0058,0.0010,0.0012</t>
-  </si>
-  <si>
-    <t>0.9865,0.0143,0.0014,0.0005</t>
-  </si>
-  <si>
-    <t>0.9893,0.0041,0.0007,0.0030</t>
-  </si>
-  <si>
-    <t>0.9869,0.0131,0.0014,0.0006</t>
-  </si>
-  <si>
-    <t>0.9920,0.0058,0.0006,0.0007</t>
-  </si>
-  <si>
-    <t>0.9868,0.0050,0.0010,0.0032</t>
-  </si>
-  <si>
-    <t>0.9862,0.0116,0.0023,0.0009</t>
-  </si>
-  <si>
-    <t>0.9954,0.0007,0.0001,0.0013</t>
-  </si>
-  <si>
-    <t>0.9949,0.0015,0.0002,0.0011</t>
-  </si>
-  <si>
-    <t>0.9936,0.0029,0.0005,0.0014</t>
-  </si>
-  <si>
-    <t>0.9911,0.0021,0.0008,0.0035</t>
-  </si>
-  <si>
-    <t>0.9905,0.0060,0.0008,0.0010</t>
-  </si>
-  <si>
-    <t>0.9959,0.0022,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9942,0.0025,0.0004,0.0010</t>
-  </si>
-  <si>
-    <t>0.9920,0.0015,0.0003,0.0030</t>
-  </si>
-  <si>
-    <t>0.0045,0.0016,0.9746,0.0298</t>
-  </si>
-  <si>
-    <t>0.1058,0.1016,0.8232,0.0078</t>
-  </si>
-  <si>
-    <t>0.6680,0.0142,0.2072,0.0660</t>
-  </si>
-  <si>
-    <t>0.3583,0.0039,0.7541,0.0028</t>
-  </si>
-  <si>
-    <t>0.0937,0.9037,0.0153,0.0007</t>
-  </si>
-  <si>
-    <t>0.1891,0.8380,0.0194,0.0009</t>
-  </si>
-  <si>
-    <t>0.3523,0.7291,0.0082,0.0029</t>
-  </si>
-  <si>
-    <t>0.0203,0.9576,0.0092,0.0056</t>
-  </si>
-  <si>
-    <t>0.3305,0.7373,0.0227,0.0012</t>
-  </si>
-  <si>
-    <t>0.0399,0.9500,0.0127,0.0003</t>
-  </si>
-  <si>
-    <t>0.4225,0.6415,0.0250,0.0016</t>
-  </si>
-  <si>
-    <t>0.6626,0.0206,0.2868,0.0360</t>
-  </si>
-  <si>
-    <t>0.3488,0.0670,0.6149,0.0551</t>
-  </si>
-  <si>
-    <t>0.6044,0.1528,0.2179,0.1471</t>
-  </si>
-  <si>
-    <t>0.6525,0.0315,0.3647,0.0077</t>
-  </si>
-  <si>
-    <t>0.1400,0.1515,0.0537,0.8764</t>
-  </si>
-  <si>
-    <t>0.0098,0.9695,0.0702,0.0026</t>
-  </si>
-  <si>
-    <t>0.0028,0.9709,0.0649,0.0375</t>
-  </si>
-  <si>
-    <t>0.0622,0.8635,0.0624,0.1305</t>
-  </si>
-  <si>
-    <t>0.0010,0.9308,0.8720,0.0008</t>
-  </si>
-  <si>
-    <t>0.1105,0.8637,0.1257,0.0018</t>
-  </si>
-  <si>
-    <t>0.6682,0.3617,0.0366,0.0022</t>
-  </si>
-  <si>
-    <t>0.7789,0.2944,0.0161,0.0007</t>
-  </si>
-  <si>
-    <t>0.9493,0.0151,0.0090,0.0228</t>
-  </si>
-  <si>
-    <t>0.9818,0.0094,0.0020,0.0038</t>
-  </si>
-  <si>
-    <t>0.9901,0.0037,0.0011,0.0024</t>
-  </si>
-  <si>
-    <t>0.9816,0.0091,0.0023,0.0047</t>
-  </si>
-  <si>
-    <t>0.9828,0.0077,0.0009,0.0056</t>
-  </si>
-  <si>
-    <t>0.9474,0.0259,0.0232,0.0058</t>
-  </si>
-  <si>
-    <t>0.9693,0.0082,0.0021,0.0137</t>
-  </si>
-  <si>
-    <t>0.9819,0.0089,0.0026,0.0035</t>
-  </si>
-  <si>
-    <t>0.0121,0.5408,0.8404,0.0022</t>
-  </si>
-  <si>
-    <t>0.0254,0.4399,0.8509,0.0025</t>
-  </si>
-  <si>
-    <t>0.0817,0.1677,0.7954,0.0057</t>
-  </si>
-  <si>
-    <t>0.0327,0.0532,0.9351,0.0042</t>
-  </si>
-  <si>
-    <t>0.3826,0.3909,0.1236,0.2604</t>
-  </si>
-  <si>
-    <t>0.6217,0.0225,0.3993,0.0190</t>
-  </si>
-  <si>
-    <t>0.7027,0.0198,0.2589,0.0296</t>
-  </si>
-  <si>
-    <t>0.5814,0.1609,0.2038,0.0845</t>
-  </si>
-  <si>
-    <t>0.0684,0.0273,0.0151,0.9557</t>
-  </si>
-  <si>
-    <t>0.0027,0.0004,0.0009,0.9976</t>
-  </si>
-  <si>
-    <t>0.0026,0.0239,0.0037,0.9962</t>
-  </si>
-  <si>
-    <t>0.0151,0.0020,0.0025,0.9918</t>
-  </si>
-  <si>
-    <t>0.0159,0.5498,0.8326,0.0173</t>
-  </si>
-  <si>
-    <t>0.9684,0.0189,0.0067,0.0041</t>
-  </si>
-  <si>
-    <t>0.5214,0.5687,0.0086,0.0042</t>
-  </si>
-  <si>
-    <t>0.9745,0.0023,0.0009,0.0189</t>
-  </si>
-  <si>
-    <t>0.8610,0.1948,0.0065,0.0027</t>
-  </si>
-  <si>
-    <t>0.9569,0.0017,0.0039,0.0216</t>
-  </si>
-  <si>
-    <t>0.4511,0.0138,0.0910,0.4182</t>
-  </si>
-  <si>
-    <t>0.9894,0.0018,0.0012,0.0034</t>
-  </si>
-  <si>
-    <t>0.0042,0.0173,0.9720,0.0349</t>
-  </si>
-  <si>
-    <t>0.8141,0.0027,0.0053,0.1858</t>
-  </si>
-  <si>
-    <t>0.7209,0.0056,0.0386,0.1835</t>
-  </si>
-  <si>
-    <t>0.1686,0.8024,0.0293,0.0306</t>
-  </si>
-  <si>
-    <t>0.6960,0.1768,0.0234,0.0749</t>
-  </si>
-  <si>
-    <t>0.9015,0.0435,0.0499,0.0052</t>
-  </si>
-  <si>
-    <t>0.5215,0.3048,0.1058,0.1623</t>
-  </si>
-  <si>
-    <t>0.8466,0.0784,0.0716,0.0112</t>
-  </si>
-  <si>
-    <t>0.7535,0.1532,0.0604,0.0627</t>
-  </si>
-  <si>
-    <t>0.9873,0.0061,0.0024,0.0019</t>
-  </si>
-  <si>
-    <t>0.9832,0.0127,0.0012,0.0021</t>
-  </si>
-  <si>
-    <t>0.9732,0.0074,0.0024,0.0128</t>
-  </si>
-  <si>
-    <t>0.9839,0.0035,0.0021,0.0048</t>
-  </si>
-  <si>
-    <t>0.9702,0.0130,0.0039,0.0087</t>
-  </si>
-  <si>
-    <t>0.9840,0.0104,0.0009,0.0040</t>
-  </si>
-  <si>
-    <t>0.9860,0.0034,0.0005,0.0059</t>
-  </si>
-  <si>
-    <t>0.9899,0.0050,0.0014,0.0015</t>
-  </si>
-  <si>
-    <t>0.3949,0.6464,0.0104,0.0077</t>
-  </si>
-  <si>
-    <t>0.8685,0.2007,0.0069,0.0012</t>
-  </si>
-  <si>
-    <t>0.4897,0.6191,0.0109,0.0012</t>
-  </si>
-  <si>
-    <t>0.9207,0.0449,0.0292,0.0155</t>
-  </si>
-  <si>
-    <t>0.9831,0.0196,0.0007,0.0009</t>
-  </si>
-  <si>
-    <t>0.9432,0.0165,0.0067,0.0375</t>
-  </si>
-  <si>
-    <t>0.9794,0.0174,0.0017,0.0027</t>
-  </si>
-  <si>
-    <t>0.8946,0.0980,0.0150,0.0078</t>
-  </si>
-  <si>
-    <t>0.0040,0.0101,0.9913,0.0017</t>
-  </si>
-  <si>
-    <t>0.9217,0.0872,0.0155,0.0018</t>
-  </si>
-  <si>
-    <t>0.0226,0.0048,0.9760,0.0027</t>
-  </si>
-  <si>
-    <t>0.0424,0.0355,0.9476,0.0033</t>
-  </si>
-  <si>
-    <t>0.3832,0.0175,0.6996,0.0087</t>
-  </si>
-  <si>
-    <t>0.0352,0.2225,0.8781,0.0204</t>
-  </si>
-  <si>
-    <t>0.0148,0.0086,0.9831,0.0011</t>
-  </si>
-  <si>
-    <t>0.0196,0.0006,0.9816,0.0033</t>
-  </si>
-  <si>
-    <t>0.0165,0.0075,0.9789,0.0031</t>
-  </si>
-  <si>
-    <t>0.5127,0.0155,0.4890,0.0317</t>
-  </si>
-  <si>
-    <t>0.3514,0.0067,0.7487,0.0039</t>
-  </si>
-  <si>
-    <t>0.6676,0.0673,0.2434,0.0316</t>
-  </si>
-  <si>
-    <t>0.1429,0.1375,0.7152,0.0024</t>
-  </si>
-  <si>
-    <t>0.1766,0.1956,0.6635,0.0085</t>
-  </si>
-  <si>
-    <t>0.3250,0.0678,0.6054,0.0075</t>
-  </si>
-  <si>
-    <t>0.5384,0.0363,0.4408,0.0787</t>
-  </si>
-  <si>
-    <t>0.6671,0.0203,0.3178,0.0362</t>
-  </si>
-  <si>
-    <t>0.6896,0.4435,0.0062,0.0023</t>
-  </si>
-  <si>
-    <t>0.9525,0.0612,0.0042,0.0021</t>
-  </si>
-  <si>
-    <t>0.8089,0.2985,0.0059,0.0010</t>
-  </si>
-  <si>
-    <t>0.9626,0.0311,0.0084,0.0023</t>
-  </si>
-  <si>
-    <t>0.9888,0.0032,0.0005,0.0034</t>
-  </si>
-  <si>
-    <t>0.6436,0.0967,0.2855,0.0237</t>
-  </si>
-  <si>
-    <t>0.6707,0.0436,0.3133,0.0105</t>
-  </si>
-  <si>
-    <t>0.5623,0.0252,0.4054,0.0591</t>
-  </si>
-  <si>
-    <t>0.5096,0.0243,0.5109,0.0183</t>
-  </si>
-  <si>
-    <t>0.4687,0.0838,0.4864,0.0389</t>
-  </si>
-  <si>
-    <t>0.0012,0.0075,0.9701,0.0546</t>
-  </si>
-  <si>
-    <t>0.0971,0.2541,0.7470,0.0452</t>
-  </si>
-  <si>
-    <t>0.0432,0.0805,0.9226,0.0039</t>
-  </si>
-  <si>
-    <t>0.1963,0.0187,0.8231,0.0057</t>
-  </si>
-  <si>
-    <t>0.0293,0.0910,0.9253,0.0060</t>
-  </si>
-  <si>
-    <t>0.9921,0.0019,0.0004,0.0020</t>
-  </si>
-  <si>
-    <t>0.9917,0.0049,0.0009,0.0009</t>
-  </si>
-  <si>
-    <t>0.9784,0.0069,0.0007,0.0071</t>
-  </si>
-  <si>
-    <t>0.9796,0.0193,0.0014,0.0037</t>
-  </si>
-  <si>
-    <t>0.9914,0.0027,0.0005,0.0027</t>
-  </si>
-  <si>
-    <t>0.9842,0.0062,0.0027,0.0027</t>
-  </si>
-  <si>
-    <t>0.9709,0.0019,0.0003,0.0289</t>
-  </si>
-  <si>
-    <t>0.9902,0.0041,0.0004,0.0018</t>
-  </si>
-  <si>
-    <t>0.6221,0.0227,0.3238,0.0692</t>
-  </si>
-  <si>
-    <t>0.4574,0.2538,0.3928,0.0617</t>
-  </si>
-  <si>
-    <t>0.7555,0.0215,0.0266,0.2117</t>
-  </si>
-  <si>
-    <t>0.0400,0.0031,0.9720,0.0015</t>
-  </si>
-  <si>
-    <t>0.0012,0.0076,0.9941,0.0023</t>
-  </si>
-  <si>
-    <t>0.0057,0.0154,0.9891,0.0011</t>
-  </si>
-  <si>
-    <t>0.0064,0.0025,0.9865,0.0034</t>
-  </si>
-  <si>
-    <t>0.3503,0.0211,0.6722,0.0219</t>
-  </si>
-  <si>
-    <t>0.0003,0.0006,0.9958,0.0056</t>
-  </si>
-  <si>
-    <t>0.0184,0.0034,0.9811,0.0018</t>
-  </si>
-  <si>
-    <t>0.3331,0.0539,0.6249,0.0255</t>
-  </si>
-  <si>
-    <t>0.7601,0.0075,0.1981,0.0224</t>
-  </si>
-  <si>
-    <t>0.6611,0.0139,0.3558,0.0125</t>
-  </si>
-  <si>
-    <t>0.6177,0.0203,0.1998,0.0981</t>
-  </si>
-  <si>
-    <t>0.9915,0.0034,0.0003,0.0017</t>
-  </si>
-  <si>
-    <t>0.9685,0.0355,0.0060,0.0013</t>
-  </si>
-  <si>
-    <t>0.9907,0.0034,0.0007,0.0020</t>
-  </si>
-  <si>
-    <t>0.9860,0.0073,0.0019,0.0017</t>
-  </si>
-  <si>
-    <t>0.9852,0.0031,0.0003,0.0067</t>
-  </si>
-  <si>
-    <t>0.9901,0.0052,0.0014,0.0014</t>
-  </si>
-  <si>
-    <t>0.9872,0.0097,0.0015,0.0012</t>
-  </si>
-  <si>
-    <t>0.9872,0.0059,0.0005,0.0026</t>
-  </si>
-  <si>
-    <t>0.2178,0.0166,0.8128,0.0035</t>
-  </si>
-  <si>
-    <t>0.0030,0.0128,0.9816,0.0121</t>
-  </si>
-  <si>
-    <t>0.0156,0.0079,0.9744,0.0062</t>
-  </si>
-  <si>
-    <t>0.1627,0.0759,0.7652,0.0249</t>
-  </si>
-  <si>
-    <t>0.0167,0.0074,0.9474,0.0399</t>
-  </si>
-  <si>
-    <t>0.3381,0.0371,0.1487,0.5404</t>
-  </si>
-  <si>
-    <t>0.4169,0.0104,0.6486,0.0095</t>
-  </si>
-  <si>
-    <t>0.1124,0.0619,0.8356,0.0343</t>
-  </si>
-  <si>
-    <t>0.7172,0.0015,0.0080,0.2761</t>
-  </si>
-  <si>
-    <t>0.0081,0.0121,0.0065,0.9925</t>
-  </si>
-  <si>
-    <t>0.0305,0.0101,0.0016,0.9874</t>
-  </si>
-  <si>
-    <t>0.0018,0.0001,0.0008,0.9980</t>
-  </si>
-  <si>
-    <t>0.0065,0.0003,0.0018,0.9944</t>
-  </si>
-  <si>
-    <t>0.5242,0.2354,0.0294,0.2859</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.8744,0.0330,0.0672,0.0099</t>
+  </si>
+  <si>
+    <t>0.0102,0.0012,0.0020,0.9942</t>
+  </si>
+  <si>
+    <t>0.5447,0.2359,0.0490,0.2642</t>
+  </si>
+  <si>
+    <t>0.0451,0.0118,0.0034,0.9807</t>
+  </si>
+  <si>
+    <t>0.9930,0.0032,0.0009,0.0009</t>
+  </si>
+  <si>
+    <t>0.9946,0.0015,0.0004,0.0014</t>
+  </si>
+  <si>
+    <t>0.9933,0.0033,0.0004,0.0009</t>
+  </si>
+  <si>
+    <t>0.9953,0.0015,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9845,0.0127,0.0015,0.0017</t>
+  </si>
+  <si>
+    <t>0.9877,0.0071,0.0011,0.0018</t>
+  </si>
+  <si>
+    <t>0.9932,0.0029,0.0010,0.0009</t>
+  </si>
+  <si>
+    <t>0.9934,0.0010,0.0002,0.0024</t>
+  </si>
+  <si>
+    <t>0.6729,0.0354,0.2727,0.0498</t>
+  </si>
+  <si>
+    <t>0.3131,0.0124,0.7467,0.0014</t>
+  </si>
+  <si>
+    <t>0.5871,0.0113,0.5163,0.0022</t>
+  </si>
+  <si>
+    <t>0.0890,0.0025,0.9450,0.0026</t>
+  </si>
+  <si>
+    <t>0.4769,0.0218,0.5641,0.0159</t>
+  </si>
+  <si>
+    <t>0.0310,0.9661,0.0091,0.0005</t>
+  </si>
+  <si>
+    <t>0.2518,0.8061,0.0127,0.0008</t>
+  </si>
+  <si>
+    <t>0.6737,0.4248,0.0126,0.0033</t>
+  </si>
+  <si>
+    <t>0.1836,0.8543,0.0041,0.0018</t>
+  </si>
+  <si>
+    <t>0.0310,0.9559,0.0165,0.0008</t>
+  </si>
+  <si>
+    <t>0.7302,0.0109,0.1638,0.0480</t>
+  </si>
+  <si>
+    <t>0.3628,0.0694,0.5612,0.0606</t>
+  </si>
+  <si>
+    <t>0.0208,0.0045,0.9705,0.0062</t>
+  </si>
+  <si>
+    <t>0.4621,0.0157,0.5306,0.0271</t>
+  </si>
+  <si>
+    <t>0.2171,0.0060,0.8456,0.0071</t>
+  </si>
+  <si>
+    <t>0.1603,0.0391,0.8092,0.0283</t>
+  </si>
+  <si>
+    <t>0.0076,0.0047,0.9837,0.0053</t>
+  </si>
+  <si>
+    <t>0.3735,0.6259,0.0220,0.0255</t>
+  </si>
+  <si>
+    <t>0.5606,0.3300,0.2047,0.0278</t>
+  </si>
+  <si>
+    <t>0.0009,0.0067,0.9837,0.0298</t>
+  </si>
+  <si>
+    <t>0.0332,0.7203,0.3724,0.0006</t>
+  </si>
+  <si>
+    <t>0.8734,0.0768,0.0149,0.0460</t>
+  </si>
+  <si>
+    <t>0.6475,0.0890,0.2777,0.0145</t>
+  </si>
+  <si>
+    <t>0.7617,0.3301,0.0113,0.0014</t>
+  </si>
+  <si>
+    <t>0.1364,0.7866,0.1948,0.0026</t>
+  </si>
+  <si>
+    <t>0.1996,0.3089,0.5386,0.0406</t>
+  </si>
+  <si>
+    <t>0.1546,0.1399,0.7459,0.0775</t>
+  </si>
+  <si>
+    <t>0.0592,0.1225,0.8792,0.0125</t>
+  </si>
+  <si>
+    <t>0.1415,0.0148,0.8381,0.0242</t>
+  </si>
+  <si>
+    <t>0.0588,0.0559,0.9184,0.0030</t>
+  </si>
+  <si>
+    <t>0.0107,0.9579,0.0935,0.0018</t>
+  </si>
+  <si>
+    <t>0.0518,0.0161,0.9499,0.0057</t>
+  </si>
+  <si>
+    <t>0.0767,0.5035,0.1646,0.7132</t>
+  </si>
+  <si>
+    <t>0.0408,0.8706,0.0967,0.0534</t>
+  </si>
+  <si>
+    <t>0.0164,0.9395,0.2185,0.0067</t>
+  </si>
+  <si>
+    <t>0.0039,0.9829,0.0974,0.0012</t>
+  </si>
+  <si>
+    <t>0.0315,0.5107,0.8045,0.0197</t>
+  </si>
+  <si>
+    <t>0.0051,0.1243,0.9695,0.0054</t>
+  </si>
+  <si>
+    <t>0.1745,0.0361,0.7955,0.0386</t>
+  </si>
+  <si>
+    <t>0.1030,0.0031,0.9254,0.0067</t>
+  </si>
+  <si>
+    <t>0.0092,0.0076,0.9841,0.0030</t>
+  </si>
+  <si>
+    <t>0.0059,0.0054,0.9880,0.0026</t>
+  </si>
+  <si>
+    <t>0.9786,0.0288,0.0022,0.0011</t>
+  </si>
+  <si>
+    <t>0.9817,0.0069,0.0046,0.0021</t>
+  </si>
+  <si>
+    <t>0.9194,0.0449,0.0350,0.0143</t>
+  </si>
+  <si>
+    <t>0.0274,0.0748,0.9631,0.0041</t>
+  </si>
+  <si>
+    <t>0.9854,0.0097,0.0013,0.0024</t>
+  </si>
+  <si>
+    <t>0.9888,0.0048,0.0008,0.0029</t>
+  </si>
+  <si>
+    <t>0.9651,0.0315,0.0036,0.0034</t>
+  </si>
+  <si>
+    <t>0.0029,0.5901,0.9166,0.0005</t>
+  </si>
+  <si>
+    <t>0.0051,0.0271,0.9708,0.0180</t>
+  </si>
+  <si>
+    <t>0.0428,0.0576,0.9242,0.0109</t>
+  </si>
+  <si>
+    <t>0.0081,0.6475,0.9073,0.0029</t>
+  </si>
+  <si>
+    <t>0.0110,0.0036,0.9888,0.0006</t>
+  </si>
+  <si>
+    <t>0.0557,0.8733,0.1033,0.0021</t>
+  </si>
+  <si>
+    <t>0.0129,0.9805,0.0040,0.0005</t>
+  </si>
+  <si>
+    <t>0.6992,0.0675,0.2359,0.0561</t>
+  </si>
+  <si>
+    <t>0.4441,0.5618,0.0559,0.0171</t>
+  </si>
+  <si>
+    <t>0.2296,0.0566,0.7477,0.0084</t>
+  </si>
+  <si>
+    <t>0.0025,0.5826,0.9209,0.0002</t>
+  </si>
+  <si>
+    <t>0.0109,0.6966,0.7941,0.0024</t>
+  </si>
+  <si>
+    <t>0.0012,0.9514,0.6791,0.0002</t>
+  </si>
+  <si>
+    <t>0.0013,0.9393,0.5887,0.0009</t>
+  </si>
+  <si>
+    <t>0.0156,0.0015,0.0352,0.9664</t>
+  </si>
+  <si>
+    <t>0.0018,0.0053,0.0005,0.9986</t>
+  </si>
+  <si>
+    <t>0.0024,0.0363,0.0005,0.9979</t>
+  </si>
+  <si>
+    <t>0.0074,0.0222,0.0024,0.9946</t>
+  </si>
+  <si>
+    <t>0.0713,0.0457,0.0213,0.9533</t>
+  </si>
+  <si>
+    <t>0.0032,0.0153,0.0012,0.9973</t>
+  </si>
+  <si>
+    <t>0.0024,0.9520,0.4792,0.0007</t>
+  </si>
+  <si>
+    <t>0.0029,0.3640,0.9710,0.0008</t>
+  </si>
+  <si>
+    <t>0.0452,0.1243,0.8985,0.0027</t>
+  </si>
+  <si>
+    <t>0.0287,0.1395,0.9143,0.0085</t>
+  </si>
+  <si>
+    <t>0.0011,0.8368,0.8153,0.0000</t>
+  </si>
+  <si>
+    <t>0.0091,0.6681,0.8337,0.0016</t>
+  </si>
+  <si>
+    <t>0.9932,0.0025,0.0004,0.0013</t>
+  </si>
+  <si>
+    <t>0.9878,0.0110,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9933,0.0059,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9912,0.0020,0.0002,0.0031</t>
+  </si>
+  <si>
+    <t>0.9638,0.0231,0.0090,0.0028</t>
+  </si>
+  <si>
+    <t>0.9939,0.0043,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9770,0.0209,0.0028,0.0019</t>
+  </si>
+  <si>
+    <t>0.9727,0.0245,0.0064,0.0013</t>
+  </si>
+  <si>
+    <t>0.9894,0.0041,0.0011,0.0022</t>
+  </si>
+  <si>
+    <t>0.9904,0.0048,0.0014,0.0011</t>
+  </si>
+  <si>
+    <t>0.9947,0.0010,0.0001,0.0014</t>
+  </si>
+  <si>
+    <t>0.9953,0.0007,0.0002,0.0017</t>
+  </si>
+  <si>
+    <t>0.9913,0.0029,0.0007,0.0025</t>
+  </si>
+  <si>
+    <t>0.9908,0.0060,0.0008,0.0009</t>
+  </si>
+  <si>
+    <t>0.9890,0.0035,0.0006,0.0025</t>
+  </si>
+  <si>
+    <t>0.9878,0.0064,0.0024,0.0019</t>
+  </si>
+  <si>
+    <t>0.0996,0.0077,0.9043,0.0241</t>
+  </si>
+  <si>
+    <t>0.1189,0.0182,0.8794,0.0043</t>
+  </si>
+  <si>
+    <t>0.6462,0.0046,0.4141,0.0100</t>
+  </si>
+  <si>
+    <t>0.2777,0.0029,0.8256,0.0042</t>
+  </si>
+  <si>
+    <t>0.3487,0.7432,0.0079,0.0010</t>
+  </si>
+  <si>
+    <t>0.0842,0.8983,0.0190,0.0023</t>
+  </si>
+  <si>
+    <t>0.0485,0.9442,0.0043,0.0015</t>
+  </si>
+  <si>
+    <t>0.1211,0.8734,0.0193,0.0057</t>
+  </si>
+  <si>
+    <t>0.0336,0.9506,0.0177,0.0014</t>
+  </si>
+  <si>
+    <t>0.0225,0.9590,0.0295,0.0014</t>
+  </si>
+  <si>
+    <t>0.9350,0.0739,0.0078,0.0027</t>
+  </si>
+  <si>
+    <t>0.6655,0.0559,0.3036,0.0288</t>
+  </si>
+  <si>
+    <t>0.3561,0.0234,0.6644,0.0160</t>
+  </si>
+  <si>
+    <t>0.6714,0.0931,0.2093,0.0779</t>
+  </si>
+  <si>
+    <t>0.5324,0.0248,0.5099,0.0145</t>
+  </si>
+  <si>
+    <t>0.5112,0.1817,0.2996,0.1420</t>
+  </si>
+  <si>
+    <t>0.0044,0.9836,0.0209,0.0035</t>
+  </si>
+  <si>
+    <t>0.0051,0.9778,0.0087,0.0302</t>
+  </si>
+  <si>
+    <t>0.0136,0.9449,0.0193,0.0794</t>
+  </si>
+  <si>
+    <t>0.0019,0.9557,0.5970,0.0076</t>
+  </si>
+  <si>
+    <t>0.1564,0.8434,0.0707,0.0019</t>
+  </si>
+  <si>
+    <t>0.6792,0.3332,0.0490,0.0042</t>
+  </si>
+  <si>
+    <t>0.4711,0.5433,0.0512,0.0026</t>
+  </si>
+  <si>
+    <t>0.9770,0.0081,0.0059,0.0048</t>
+  </si>
+  <si>
+    <t>0.9729,0.0082,0.0074,0.0073</t>
+  </si>
+  <si>
+    <t>0.9779,0.0093,0.0054,0.0044</t>
+  </si>
+  <si>
+    <t>0.9739,0.0118,0.0037,0.0049</t>
+  </si>
+  <si>
+    <t>0.9836,0.0052,0.0005,0.0068</t>
+  </si>
+  <si>
+    <t>0.9440,0.0383,0.0136,0.0068</t>
+  </si>
+  <si>
+    <t>0.9692,0.0073,0.0026,0.0151</t>
+  </si>
+  <si>
+    <t>0.9831,0.0075,0.0028,0.0025</t>
+  </si>
+  <si>
+    <t>0.0234,0.3586,0.8673,0.0031</t>
+  </si>
+  <si>
+    <t>0.0150,0.2314,0.9019,0.0006</t>
+  </si>
+  <si>
+    <t>0.0429,0.0793,0.9110,0.0032</t>
+  </si>
+  <si>
+    <t>0.0344,0.1839,0.8471,0.0027</t>
+  </si>
+  <si>
+    <t>0.5661,0.0583,0.4103,0.0474</t>
+  </si>
+  <si>
+    <t>0.6622,0.1753,0.1847,0.0298</t>
+  </si>
+  <si>
+    <t>0.4277,0.0023,0.7409,0.0032</t>
+  </si>
+  <si>
+    <t>0.5267,0.1687,0.3458,0.0773</t>
+  </si>
+  <si>
+    <t>0.0360,0.0043,0.0061,0.9777</t>
+  </si>
+  <si>
+    <t>0.0009,0.0004,0.0002,0.9994</t>
+  </si>
+  <si>
+    <t>0.0030,0.0018,0.0027,0.9961</t>
+  </si>
+  <si>
+    <t>0.0098,0.0012,0.0014,0.9944</t>
+  </si>
+  <si>
+    <t>0.0022,0.9268,0.5379,0.0007</t>
+  </si>
+  <si>
+    <t>0.9795,0.0125,0.0039,0.0021</t>
+  </si>
+  <si>
+    <t>0.7134,0.3339,0.0226,0.0058</t>
+  </si>
+  <si>
+    <t>0.9560,0.0475,0.0025,0.0045</t>
+  </si>
+  <si>
+    <t>0.9246,0.0820,0.0099,0.0034</t>
+  </si>
+  <si>
+    <t>0.9651,0.0098,0.0037,0.0160</t>
+  </si>
+  <si>
+    <t>0.8296,0.0084,0.0447,0.0764</t>
+  </si>
+  <si>
+    <t>0.9838,0.0077,0.0013,0.0034</t>
+  </si>
+  <si>
+    <t>0.0068,0.0594,0.9537,0.0536</t>
+  </si>
+  <si>
+    <t>0.8493,0.0077,0.0096,0.1226</t>
+  </si>
+  <si>
+    <t>0.8617,0.0057,0.0146,0.0932</t>
+  </si>
+  <si>
+    <t>0.5244,0.4389,0.0565,0.0379</t>
+  </si>
+  <si>
+    <t>0.8700,0.0627,0.0348,0.0164</t>
+  </si>
+  <si>
+    <t>0.5909,0.3989,0.0984,0.0204</t>
+  </si>
+  <si>
+    <t>0.5276,0.2930,0.2832,0.0240</t>
+  </si>
+  <si>
+    <t>0.6059,0.3140,0.1298,0.0122</t>
+  </si>
+  <si>
+    <t>0.8049,0.1483,0.0621,0.0130</t>
+  </si>
+  <si>
+    <t>0.9817,0.0114,0.0015,0.0027</t>
+  </si>
+  <si>
+    <t>0.9867,0.0033,0.0005,0.0047</t>
+  </si>
+  <si>
+    <t>0.9865,0.0027,0.0005,0.0056</t>
+  </si>
+  <si>
+    <t>0.9813,0.0039,0.0010,0.0085</t>
+  </si>
+  <si>
+    <t>0.9853,0.0079,0.0012,0.0029</t>
+  </si>
+  <si>
+    <t>0.9825,0.0077,0.0033,0.0030</t>
+  </si>
+  <si>
+    <t>0.9887,0.0043,0.0005,0.0024</t>
+  </si>
+  <si>
+    <t>0.9868,0.0044,0.0013,0.0033</t>
+  </si>
+  <si>
+    <t>0.3166,0.7690,0.0058,0.0044</t>
+  </si>
+  <si>
+    <t>0.6651,0.3716,0.0280,0.0013</t>
+  </si>
+  <si>
+    <t>0.7458,0.3574,0.0104,0.0021</t>
+  </si>
+  <si>
+    <t>0.7256,0.2352,0.1175,0.0234</t>
+  </si>
+  <si>
+    <t>0.9492,0.0644,0.0052,0.0017</t>
+  </si>
+  <si>
+    <t>0.8776,0.0209,0.0050,0.0536</t>
+  </si>
+  <si>
+    <t>0.9825,0.0135,0.0029,0.0006</t>
+  </si>
+  <si>
+    <t>0.9367,0.0625,0.0061,0.0068</t>
+  </si>
+  <si>
+    <t>0.0043,0.0200,0.9908,0.0020</t>
+  </si>
+  <si>
+    <t>0.9273,0.0533,0.0205,0.0050</t>
+  </si>
+  <si>
+    <t>0.0090,0.0052,0.9873,0.0017</t>
+  </si>
+  <si>
+    <t>0.0339,0.0155,0.9605,0.0040</t>
+  </si>
+  <si>
+    <t>0.0251,0.0034,0.9797,0.0013</t>
+  </si>
+  <si>
+    <t>0.0537,0.3325,0.7749,0.0401</t>
+  </si>
+  <si>
+    <t>0.0316,0.0025,0.9583,0.0128</t>
+  </si>
+  <si>
+    <t>0.0029,0.0005,0.9961,0.0006</t>
+  </si>
+  <si>
+    <t>0.0151,0.0033,0.9856,0.0013</t>
+  </si>
+  <si>
+    <t>0.2216,0.0693,0.7133,0.0191</t>
+  </si>
+  <si>
+    <t>0.3429,0.0942,0.5589,0.0087</t>
+  </si>
+  <si>
+    <t>0.8310,0.0182,0.1382,0.0118</t>
+  </si>
+  <si>
+    <t>0.2148,0.4413,0.3391,0.0072</t>
+  </si>
+  <si>
+    <t>0.4310,0.0974,0.5103,0.0060</t>
+  </si>
+  <si>
+    <t>0.7205,0.0038,0.3888,0.0039</t>
+  </si>
+  <si>
+    <t>0.5228,0.1217,0.4265,0.0704</t>
+  </si>
+  <si>
+    <t>0.5531,0.1551,0.3440,0.0733</t>
+  </si>
+  <si>
+    <t>0.9630,0.0514,0.0028,0.0009</t>
+  </si>
+  <si>
+    <t>0.2539,0.7843,0.0051,0.0072</t>
+  </si>
+  <si>
+    <t>0.9158,0.1058,0.0092,0.0029</t>
+  </si>
+  <si>
+    <t>0.9840,0.0104,0.0014,0.0027</t>
+  </si>
+  <si>
+    <t>0.9066,0.1335,0.0052,0.0019</t>
+  </si>
+  <si>
+    <t>0.6529,0.0307,0.3351,0.0175</t>
+  </si>
+  <si>
+    <t>0.8404,0.0054,0.2051,0.0030</t>
+  </si>
+  <si>
+    <t>0.3699,0.0415,0.0309,0.6376</t>
+  </si>
+  <si>
+    <t>0.5881,0.0383,0.3842,0.0300</t>
+  </si>
+  <si>
+    <t>0.7736,0.0532,0.1447,0.0225</t>
+  </si>
+  <si>
+    <t>0.0158,0.0100,0.9602,0.0230</t>
+  </si>
+  <si>
+    <t>0.1794,0.0325,0.8066,0.0051</t>
+  </si>
+  <si>
+    <t>0.0509,0.1049,0.9030,0.0028</t>
+  </si>
+  <si>
+    <t>0.0180,0.0632,0.9533,0.0099</t>
+  </si>
+  <si>
+    <t>0.0098,0.0469,0.9566,0.0151</t>
+  </si>
+  <si>
+    <t>0.9888,0.0038,0.0012,0.0026</t>
+  </si>
+  <si>
+    <t>0.9883,0.0041,0.0018,0.0024</t>
+  </si>
+  <si>
+    <t>0.9835,0.0111,0.0013,0.0022</t>
+  </si>
+  <si>
+    <t>0.9874,0.0060,0.0020,0.0019</t>
+  </si>
+  <si>
+    <t>0.9946,0.0039,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9029,0.0929,0.0157,0.0122</t>
+  </si>
+  <si>
+    <t>0.9891,0.0038,0.0005,0.0028</t>
+  </si>
+  <si>
+    <t>0.9910,0.0030,0.0008,0.0018</t>
+  </si>
+  <si>
+    <t>0.2046,0.0456,0.7351,0.0794</t>
+  </si>
+  <si>
+    <t>0.4782,0.0299,0.5585,0.0209</t>
+  </si>
+  <si>
+    <t>0.9207,0.0335,0.0080,0.0405</t>
+  </si>
+  <si>
+    <t>0.0087,0.0043,0.9855,0.0032</t>
+  </si>
+  <si>
+    <t>0.0113,0.0606,0.9587,0.0144</t>
+  </si>
+  <si>
+    <t>0.2069,0.0085,0.8500,0.0021</t>
+  </si>
+  <si>
+    <t>0.0008,0.0013,0.9941,0.0057</t>
+  </si>
+  <si>
+    <t>0.2332,0.0309,0.7387,0.0089</t>
+  </si>
+  <si>
+    <t>0.0062,0.0133,0.9797,0.0086</t>
+  </si>
+  <si>
+    <t>0.0099,0.0024,0.9887,0.0019</t>
+  </si>
+  <si>
+    <t>0.0440,0.0410,0.9297,0.0045</t>
+  </si>
+  <si>
+    <t>0.7628,0.0091,0.2798,0.0055</t>
+  </si>
+  <si>
+    <t>0.6516,0.0142,0.3029,0.0388</t>
+  </si>
+  <si>
+    <t>0.6186,0.0208,0.2194,0.0971</t>
+  </si>
+  <si>
+    <t>0.9880,0.0048,0.0006,0.0027</t>
+  </si>
+  <si>
+    <t>0.9890,0.0058,0.0007,0.0019</t>
+  </si>
+  <si>
+    <t>0.9948,0.0013,0.0004,0.0013</t>
+  </si>
+  <si>
+    <t>0.9834,0.0100,0.0032,0.0017</t>
+  </si>
+  <si>
+    <t>0.9916,0.0023,0.0003,0.0026</t>
+  </si>
+  <si>
+    <t>0.9950,0.0023,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.9930,0.0035,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9928,0.0029,0.0004,0.0011</t>
+  </si>
+  <si>
+    <t>0.1133,0.0577,0.8468,0.0110</t>
+  </si>
+  <si>
+    <t>0.0190,0.0430,0.9616,0.0016</t>
+  </si>
+  <si>
+    <t>0.0379,0.0239,0.9539,0.0029</t>
+  </si>
+  <si>
+    <t>0.1463,0.0177,0.8526,0.0083</t>
+  </si>
+  <si>
+    <t>0.0071,0.0055,0.9854,0.0034</t>
+  </si>
+  <si>
+    <t>0.1167,0.0149,0.2369,0.6660</t>
+  </si>
+  <si>
+    <t>0.1669,0.0044,0.8684,0.0088</t>
+  </si>
+  <si>
+    <t>0.0474,0.0740,0.6165,0.3777</t>
+  </si>
+  <si>
+    <t>0.5746,0.0061,0.0201,0.4369</t>
+  </si>
+  <si>
+    <t>0.0054,0.0335,0.0015,0.9957</t>
+  </si>
+  <si>
+    <t>0.0161,0.0312,0.0025,0.9905</t>
+  </si>
+  <si>
+    <t>0.0007,0.0008,0.0036,0.9979</t>
+  </si>
+  <si>
+    <t>0.0016,0.0013,0.0002,0.9991</t>
+  </si>
+  <si>
+    <t>0.6235,0.0871,0.1029,0.2639</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1993,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2133,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2147,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,10 +2158,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,10 +2186,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2231,7 @@
         <v>259</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2267,7 +2273,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,10 +2284,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,10 +2368,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,7 +2385,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2413,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,7 +2441,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,7 +2455,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,7 +2483,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2511,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2578,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,10 +2606,10 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,10 +2634,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2651,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2819,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,10 +2914,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,10 +2928,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2959,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2973,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,10 +2984,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,10 +2998,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,10 +3096,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3113,7 @@
         <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3127,7 @@
         <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3141,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3155,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,7 +3169,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3435,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,10 +3544,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3561,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3575,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3583,7 +3589,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3600,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,10 +3614,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3673,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3701,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,10 +3712,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,10 +3838,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3855,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3869,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3883,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3897,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3911,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,10 +3922,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4009,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,10 +4034,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4065,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4093,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,10 +4160,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4199,7 +4205,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4359,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,7 +4373,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,10 +4384,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4395,7 +4401,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4457,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,10 +4594,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4619,7 +4625,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4636,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4647,7 +4653,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,10 +4664,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4681,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,7 +4695,7 @@
         <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4709,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,10 +4720,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4737,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4765,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4779,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4793,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,10 +4804,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,10 +4818,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4835,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4863,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4877,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4905,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,10 +5028,10 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5042,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5171,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5199,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5403,7 +5409,7 @@
         <v>260</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5451,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5521,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
